--- a/光伏配储项目/电价数据/2026/威光站.xlsx
+++ b/光伏配储项目/电价数据/2026/威光站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.42178</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38452</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.79383</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.46664</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.48815</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.42877</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.43913</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.3898</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.3852</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.37467</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.37681</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.36753</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.36562</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.36348</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.37143</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.36981</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.35829</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.38187</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.38531</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.37907</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.39466</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.41083</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.24555</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.12289</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>-0.01654</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.06434000000000001</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.06822</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.05371</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29377</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.32757</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.5161100000000001</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.56143</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.74322</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.14726</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39651</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.395</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43421</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44104</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.6683600000000001</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.89411</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.50431</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.21786</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.35232</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.17079</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.04718</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.31406</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.41625</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.45718</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.7095900000000001</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.76149</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.13856</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.95301</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.91286</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.80833</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.77088</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5201699999999999</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.49113</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.47124</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.42142</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.43178</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.73424</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.91077</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9767899999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.51461</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.54459</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5220499999999999</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5222100000000001</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.5034</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40847</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.48379</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38475</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.39418</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.53385</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.40787</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.39408</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.3938</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.49686</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.44461</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.44618</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.43775</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.52518</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.71906</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.62222</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.58367</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.56412</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.58746</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38598</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.3664</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.39869</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.49437</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.25632</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30805</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29926</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.16763</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>-0.02201</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.39215</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.37427</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.5381</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.17777</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>-0.0141</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.30403</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.32541</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.6069199999999999</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.77507</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.80914</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.19438</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.43264</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.14574</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.86761</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.23378</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.12986</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.38636</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.14063</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.11417</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.67249</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.00767</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.93037</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.98588</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.8261900000000001</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.47011</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.4557</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>1.44752</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>1.50547</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.4552</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43322</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44923</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.38007</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33554</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5235299999999999</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.50219</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.50219</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37434</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.45363</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.42178</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37489</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39611</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38977</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36828</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43944</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45675</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37599</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.40469</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.3732799999999999</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.3737200000000001</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36669</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.40927</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.38158</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.40363</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.40855</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.48815</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45169</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44925</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40116</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36711</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.22976</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32104</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.80367</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>-0.01279</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.44863</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38867</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.43671</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.34817</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.44403</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.34707</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.94853</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.01307</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.33214</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.63047</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.67065</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.47046</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5076499999999999</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.28989</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.54708</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.70873</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.65294</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.8897200000000001</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.55734</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.43968</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.5111</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6319400000000001</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.59289</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.66672</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.48177</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.19146</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.01489</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>1.17306</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.29921</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.4381</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.46231</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.40018</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34305</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.52515</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.51152</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.4462</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39757</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39649</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40048</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37305</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36442</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.39685</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39426</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45999</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36677</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35368</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.37107</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36375</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36527</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35273</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.3416</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35543</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.39287</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39472</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35404</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.3818</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34717</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39855</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42225</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.43726</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.41828</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34206</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.35595</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.30778</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.6005499999999999</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.30334</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.40844</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.31905</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.22198</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.19538</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.32554</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.36721</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.30838</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.40999</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6443099999999999</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.30268</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>1.08114</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.9217799999999999</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.41231</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.7323500000000001</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.33578</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.45185</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.07941</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.52935</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.4511</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.47562</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.4045299999999999</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.57548</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>1.16153</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.19619</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.56759</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.69025</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.5266000000000001</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.49841</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50443</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.4502</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.42745</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.41879</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.42858</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.37469</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32132</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3128</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.33248</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37961</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32716</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31763</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31891</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31224</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30907</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30851</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31436</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31734</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.29386</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.30691</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.31749</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.2866</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.30585</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.30056</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.25752</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.03432</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.1333</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.03897</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.02299</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.02514</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.2341</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29636</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29577</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.3744</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.6142000000000001</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.59276</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.6052799999999999</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.49793</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.41362</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.6256900000000001</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.56714</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.6019500000000001</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.5971599999999999</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.45757</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.52459</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.56697</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.81904</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.41056</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.38671</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.35335</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.37967</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.4953</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.37533</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.82698</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1.32415</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1.17639</v>
+      </c>
+      <c r="G122" t="n">
+        <v>1.26122</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.49474</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.66299</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.48554</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.9367300000000001</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.44534</v>
+      </c>
+      <c r="M122" t="n">
+        <v>1.06868</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.8126599999999999</v>
+      </c>
+      <c r="O122" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.4753500000000001</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.48045</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.46318</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.93848</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.67991</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.85012</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.87686</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.43626</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.95628</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.46348</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.7222499999999999</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.68987</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.48017</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.94652</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.52516</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10156</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04283</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04489</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.2916</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00555</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.19768</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04502</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.26284</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.14069</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04334</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04548</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04338</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.01182</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05183</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19974</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.35385</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.39396</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.48287</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.46005</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.41948</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.45089</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.33404</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.59233</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.4479</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32638</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27068</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38133</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.43054</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.46035</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41842</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39798</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15655</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62203</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78572</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92038</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9141900000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86286</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29619</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88746</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18705</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8697</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.61137</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33081</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03289</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307500000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79096</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.55521</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77295</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77752</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87385</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49312</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39985</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44991</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20696</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87882</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55101</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62181</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43713</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45125</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42031</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.45341</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.43056</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.41562</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.41527</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.5310900000000001</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.5854</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.42957</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.4571</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.44839</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.44266</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.7777000000000001</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.48091</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.49623</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.55589</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.7349199999999999</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>1.15474</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.9160700000000001</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.81003</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>1.28832</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.89085</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47606</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.96823</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>1.18396</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.77659</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.9569099999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87503</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.96146</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.39439</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.3646</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.44616</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.6001000000000001</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.4072</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.4374</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.3777799999999999</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.39869</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.33673</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.51405</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.30127</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.44323</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.36085</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.34828</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29597</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.3946</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.89615</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.51427</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.54196</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.5168400000000001</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.58796</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.51114</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.48249</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.5492999999999999</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.46842</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.46632</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.45861</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.5239400000000001</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.5164</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.87124</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.88401</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>1.06675</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.89535</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.7607699999999999</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.73839</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.48163</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1.04371</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.58623</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.9048200000000001</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.83539</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.73638</v>
+      </c>
+      <c r="H125" t="n">
+        <v>1.06315</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.67686</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.82455</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.54664</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.5841900000000001</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.50726</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.57262</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.45806</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.58317</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.5362899999999999</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.43723</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.86199</v>
+      </c>
+      <c r="U125" t="n">
+        <v>1.28705</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.58369</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.77673</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.54137</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.57887</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.6038600000000001</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.68489</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.60654</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.60609</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.46933</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.40683</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.48988</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.48805</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.4777</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.53116</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.36432</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.35229</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.30708</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.1102</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.26217</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>-0.03184</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30407</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.25789</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.27506</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.15157</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.26334</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26051</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20381</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.29124</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.37025</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.38376</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.37303</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.45412</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.44847</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.38185</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>1.00531</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.39767</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.47149</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.42015</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.4889</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.37927</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29619</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.5400900000000001</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.26346</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.56547</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.48184</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.48493</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.4887</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.28493</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.60617</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.46618</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.53589</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.44668</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.5656599999999999</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.47486</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.69079</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.51676</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>1.05809</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.47363</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.49619</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.43533</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.4779</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.59335</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.53387</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.79612</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.49233</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.8118</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.83168</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.90649</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.14521</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.62937</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.34997</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.8585900000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.95225</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.80857</v>
+      </c>
+      <c r="I126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J126" t="n">
+        <v>1.44949</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.5975499999999999</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.64967</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.58477</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.83096</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.56031</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.55214</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.7862</v>
+      </c>
+      <c r="R126" t="n">
+        <v>1.27749</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.55116</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.5751799999999999</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.90444</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.57364</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.5207999999999999</v>
+      </c>
+      <c r="X126" t="n">
+        <v>1.02182</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>1.13462</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.53363</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.5590700000000001</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>1.04095</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.54147</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.87072</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>1.02413</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.5361900000000001</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.89854</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.63313</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.49125</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>1.12307</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.43508</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.78043</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.62921</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.41033</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.50384</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.45119</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.38663</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.10621</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.49256</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25509</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.39535</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.19502</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27725</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.03829</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.39322</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30327</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26879</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26494</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28748</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.42194</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.48182</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.4060299999999999</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.53851</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.5293099999999999</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.7156399999999999</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.71662</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.4682</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.49554</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.46434</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.6101</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.5177200000000001</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.47782</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.7113400000000001</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.5620700000000001</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.49803</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.48387</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.13112</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>1.04424</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.08107</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>1.02298</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.6615</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.83968</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.68991</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.62713</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.51003</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.6519199999999999</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.49729</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.63335</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>1.08499</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.7082000000000001</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.75727</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1.11373</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.46294</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.92788</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.93253</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.9572999999999999</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.92072</v>
+      </c>
+      <c r="L127" t="n">
+        <v>1.06543</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.64964</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.6525299999999999</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.65465</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.45298</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.44898</v>
+      </c>
+      <c r="R127" t="n">
+        <v>1.05862</v>
+      </c>
+      <c r="S127" t="n">
+        <v>1.05797</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.44822</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.46365</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.44435</v>
+      </c>
+      <c r="W127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.91983</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>1.26221</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.9941599999999999</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>1.29517</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>1.21686</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.71309</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.47221</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.8591799999999999</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.5960700000000001</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>1.1019</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.44857</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.51327</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>1.00804</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.62112</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.66892</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.6844</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.84387</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.39934</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.05889</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28653</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.10786</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>-0.01161</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.00628</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.27134</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.02602</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.20326</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>-0.00831</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25781</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.08689</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>-0.03316</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.1901</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>-0.03353</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.53649</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.4602</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.63307</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.49936</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.65527</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.60558</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.6505</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.78827</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.70584</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.53644</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.7948200000000001</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.65111</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.76918</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>1.11151</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.8487</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.7847000000000001</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.8594299999999999</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.8178099999999999</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>1.0834</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>1.06266</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>1.03977</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>1.05644</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.57147</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.5348999999999999</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.52246</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.5276900000000001</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.52127</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.67916</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.67206</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.76771</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.637</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.55099</v>
+      </c>
+      <c r="C128" t="n">
+        <v>1.50996</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.51647</v>
+      </c>
+      <c r="E128" t="n">
+        <v>1.1468</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.9165399999999999</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.88285</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.6765</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.7244299999999999</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.71225</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.76501</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.50739</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.68733</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.59635</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.75046</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.65442</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.73388</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.58296</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.56863</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.5940299999999999</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.5569700000000001</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.53706</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.5572699999999999</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.53706</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.56363</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>1.0892</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.6905399999999999</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.72199</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.61836</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.5078199999999999</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.5525</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.50801</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.4709100000000001</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.51591</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.52473</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.49273</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.36448</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.41305</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31534</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.34478</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.3429700000000001</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.23854</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.25946</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.18827</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.14533</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.43253</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.18295</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24935</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.21709</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30085</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31498</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.28407</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.48641</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31287</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.24534</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>1.5934</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.43041</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.4538</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.80603</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.56167</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.50241</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>1.02328</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.5293600000000001</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.6334500000000001</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.49924</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.47348</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.5789</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.5446599999999999</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.53935</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.47335</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.46538</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.52838</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.6208899999999999</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>1.15007</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.6027</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.41037</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.66925</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.44174</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.5542699999999999</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.5190900000000001</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.5784600000000001</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.5742699999999999</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.79379</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.46323</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.48304</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.57009</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.5860700000000001</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.53554</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.7772100000000001</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.6859</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.7054</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.5442</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.59656</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.42794</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.61461</v>
+      </c>
+      <c r="D129" t="n">
+        <v>1.38979</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.49856</v>
+      </c>
+      <c r="F129" t="n">
+        <v>1.37491</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.67677</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.5615</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.7240800000000001</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.64797</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.63101</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.55426</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.57948</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.55232</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.56475</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.4748</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.5870299999999999</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.54679</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.54228</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.4710299999999999</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.46649</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.53055</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.4678</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.46311</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.53942</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.54179</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.5826</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.76949</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.50792</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.67814</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.6386000000000001</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.46832</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.53137</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.60188</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.5694400000000001</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.26385</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.56247</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.81071</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.50624</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.64425</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.61453</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.49921</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.5721000000000001</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.61033</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.48778</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.55396</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.49394</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.6472899999999999</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.26713</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.26759</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.29582</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.51374</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.9883200000000001</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30038</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.37912</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.7289099999999999</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.51361</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.4927</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.5179199999999999</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.50576</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.46904</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.62463</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.5203099999999999</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.43346</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.51781</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.81126</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.65808</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.49496</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.50842</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.5591</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.46861</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.34878</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.45883</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.7336900000000001</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.60765</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.51935</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.5980700000000001</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.5792999999999999</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.84837</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.5174299999999999</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>1.64076</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.50581</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.64113</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.38557</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.5874400000000001</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.50086</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.40491</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.5241</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.61295</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.62525</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.94059</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.69153</v>
+      </c>
+      <c r="D130" t="n">
+        <v>1.03838</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.5373300000000001</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.6272000000000001</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.5734600000000001</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.6426499999999999</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.75803</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.97035</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.9116599999999999</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.5869099999999999</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.62012</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.5690700000000001</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.5737000000000001</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.5683400000000001</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.55389</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.92736</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.45284</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.93638</v>
+      </c>
+      <c r="U130" t="n">
+        <v>1.067</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.68775</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.44807</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.45124</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.6023200000000001</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.93611</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.93586</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.9100900000000001</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.98787</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>1.14076</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>1.09492</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.93768</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.7344299999999999</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.56396</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.48391</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.50949</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.51169</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.4642</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.47217</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.7356</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.47586</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.4182</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.47623</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.53066</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.55025</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.56572</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.56286</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.44798</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.5327000000000001</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.41449</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.52861</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.43011</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.48597</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.4587</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.46164</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.46691</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.54392</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.5318099999999999</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.52234</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.55855</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.5093299999999999</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.49144</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.92688</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.5963200000000001</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.4757</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.45086</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.7463099999999999</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.6596799999999999</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.5445</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.53316</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.4866</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.50743</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.5512699999999999</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.56826</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>1.10697</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.5638300000000001</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.88518</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.47685</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.7502300000000001</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.49848</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.49039</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.7609400000000001</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.49158</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.73914</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.49171</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.8577100000000001</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.80431</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.50218</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>1.11913</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.48609</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.82167</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.49917</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>1.01789</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>1.15148</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.4799</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.84751</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.4795</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.54371</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.48017</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.47917</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.48021</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.48114</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.48062</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.47983</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.64727</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.47917</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.47602</v>
+      </c>
+      <c r="L131" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.47681</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.6083200000000001</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.62683</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.61175</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.46936</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.46983</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.57377</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.7425900000000001</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.45417</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.5781799999999999</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.46937</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.63495</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.55929</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.6283099999999999</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.47483</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.56011</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.60839</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.6105499999999999</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.4661</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.5990800000000001</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.5632999999999999</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.6282300000000001</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.54686</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.5821499999999999</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.56191</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.47459</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.47855</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.45357</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.42829</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.36325</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.39392</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.39585</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.37008</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.42819</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.41583</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.49119</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.39806</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.36172</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.39511</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.38878</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.34846</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.36761</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.41741</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.46183</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.49745</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.41311</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.45162</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.52352</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.48346</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.51455</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.48644</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.48942</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.49954</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.47973</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.55159</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.48173</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.54716</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.48856</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.49358</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.4785</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.61922</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.71705</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.65604</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.64478</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.85699</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.5536</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.63389</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.50558</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.78487</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.94179</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.87609</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>1.05015</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.83363</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.48015</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.48421</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.4889</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.46933</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.55126</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.54108</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.5062300000000001</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.57953</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.49199</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.48913</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.4888</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.49196</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.48804</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.5561200000000001</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.48892</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.48278</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.48993</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.5688799999999999</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.48606</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.48202</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.5677000000000001</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.48942</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.48975</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.47748</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.7474500000000001</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.48872</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.48645</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.49001</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.49001</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.68429</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.49582</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.5098199999999999</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.48651</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.48642</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.48113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.48182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.48785</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.48562</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.4248</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.51136</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.48685</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.6342000000000001</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.25181</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.04331</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31005</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28057</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.27723</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.01465</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.27379</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.29079</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.29335</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.20963</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.06073</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.15912</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.21882</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.20587</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.27362</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.25291</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.29082</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.40302</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.57598</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.26388</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.28514</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.45695</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.49708</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.51259</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.62074</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.48725</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.5316900000000001</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.40229</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.52388</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.49804</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.74837</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.9956699999999999</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.20915</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.00369</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.6090099999999999</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.80043</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.75814</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.7887000000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>1.44225</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.9646699999999999</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>1.32023</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>1.66914</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.6446900000000001</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.55668</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.5643899999999999</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.9224199999999999</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>1.29026</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.9195099999999999</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.8608300000000001</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.6298400000000001</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.50319</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.58513</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.55767</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="C133" t="n">
+        <v>1.17666</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.58685</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.31007</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.83263</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.84161</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.7595499999999999</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.81471</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.7819299999999999</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.83425</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.73411</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.5228700000000001</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.7405900000000001</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.73487</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.68129</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.51624</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.88649</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.7265900000000001</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.8783500000000001</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.7394700000000001</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.88597</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.81675</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.8518600000000001</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.8521799999999999</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>1.17757</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>1.10519</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>1.70419</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>1.32796</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>1.05117</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>1.29236</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>1.03724</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.58289</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.51537</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.5437799999999999</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.56233</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.5988600000000001</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.6151799999999999</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.68008</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.56276</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.6495700000000001</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.48794</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.7442300000000001</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.8610800000000001</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.73799</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.55145</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.4987</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.49701</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33597</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.40554</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.65666</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.3767</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.71309</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.24527</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.46278</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.50073</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.78586</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.45312</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.42166</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.47729</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.47507</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.60562</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.48886</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.84873</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.81223</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.83205</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.70741</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.87012</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.6449600000000001</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.93641</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.9197799999999999</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.20317</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.04063</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.34035</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.35489</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.55941</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.65335</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.8962899999999999</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.7503200000000001</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.80052</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.22088</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.25939</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1.19446</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>1.14719</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>1.13287</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.82704</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.51769</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.88762</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.9621499999999999</v>
+      </c>
+      <c r="F134" t="n">
+        <v>1.04882</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.56259</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.5525399999999999</v>
+      </c>
+      <c r="I134" t="n">
+        <v>1.00585</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.54426</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.77038</v>
+      </c>
+      <c r="L134" t="n">
+        <v>1.26945</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.8746799999999999</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.8944299999999999</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.7589900000000001</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.72221</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.6539199999999999</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.66714</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.48835</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.48515</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.49412</v>
+      </c>
+      <c r="V134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.7825800000000001</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.68896</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.48801</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.49412</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.86248</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.85233</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.68877</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.48954</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.48331</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.50766</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.50341</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.8115800000000001</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.50278</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.52771</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.70887</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.51489</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.5632699999999999</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.45409</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.64942</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.66246</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.74266</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.52639</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.55128</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.28612</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.02666</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.37354</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.36293</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.61633</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37512</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.5766100000000001</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.41196</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.78913</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.96451</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.48321</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>-0.02801</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>-0.0362</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32379</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.51217</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.47702</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.44882</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.46132</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.65504</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.6531</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.7247400000000001</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.5187999999999999</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.9035</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>1.02377</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.5677000000000001</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.54564</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>1.03625</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.5362</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.7614</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>1.09058</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>1.1342</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>1.13644</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.99012</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.71063</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.98929</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.50642</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.92137</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.48843</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.74349</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.4899</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.88039</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>1.23937</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.55341</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>1.18086</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>1.27318</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>1.22842</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>1.02795</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.94024</v>
+      </c>
+      <c r="C135" t="n">
+        <v>1.3356</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.10397</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.9974</v>
+      </c>
+      <c r="F135" t="n">
+        <v>1.09758</v>
+      </c>
+      <c r="G135" t="n">
+        <v>1.02405</v>
+      </c>
+      <c r="H135" t="n">
+        <v>1.06813</v>
+      </c>
+      <c r="I135" t="n">
+        <v>1.14221</v>
+      </c>
+      <c r="J135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.7689900000000001</v>
+      </c>
+      <c r="L135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N135" t="n">
+        <v>1.14046</v>
+      </c>
+      <c r="O135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.97678</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.47962</v>
+      </c>
+      <c r="R135" t="n">
+        <v>1.14124</v>
+      </c>
+      <c r="S135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T135" t="n">
+        <v>1.08551</v>
+      </c>
+      <c r="U135" t="n">
+        <v>1.11198</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.96284</v>
+      </c>
+      <c r="W135" t="n">
+        <v>1.09743</v>
+      </c>
+      <c r="X135" t="n">
+        <v>1.11233</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>1.12723</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>1.78793</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>1.14214</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>1.7824</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>1.20178</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.9047799999999999</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>1.0409</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.44072</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.47925</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.82765</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.63544</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.72126</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.5603899999999999</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.19397</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.6651900000000001</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.22584</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.23542</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.69272</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.39673</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>1.63218</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.22791</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.25666</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>-0.03466</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>-0.01255</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27678</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.18249</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.16863</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.5218700000000001</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.4933</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.50484</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.6521399999999999</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.66428</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.55486</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.5281699999999999</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.60294</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.55563</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.48181</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.68647</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.57347</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.85803</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.69345</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.81036</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.82052</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.66464</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.44306</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.89467</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.70843</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.85702</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.76437</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>1.04517</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>1.07404</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>1.0428</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.8728400000000001</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.8620800000000001</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.7843</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.7244700000000001</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.8415499999999999</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>1.19865</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>1.23051</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.7463200000000001</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>1.13935</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.65426</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>1.14079</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.86178</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.7188</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.70231</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.60566</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.61181</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.60777</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.6224299999999999</v>
+      </c>
+      <c r="H136" t="n">
+        <v>1.59196</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.9195800000000001</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.90663</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.53435</v>
+      </c>
+      <c r="L136" t="n">
+        <v>1.68554</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.76788</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.6997599999999999</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.72068</v>
+      </c>
+      <c r="P136" t="n">
+        <v>1.49573</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>1.74707</v>
+      </c>
+      <c r="R136" t="n">
+        <v>1.6875</v>
+      </c>
+      <c r="S136" t="n">
+        <v>1.68751</v>
+      </c>
+      <c r="T136" t="n">
+        <v>1.66819</v>
+      </c>
+      <c r="U136" t="n">
+        <v>1.66819</v>
+      </c>
+      <c r="V136" t="n">
+        <v>1.67977</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.76885</v>
+      </c>
+      <c r="X136" t="n">
+        <v>1.72312</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>1.66819</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>1.67011</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.88479</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>1.74806</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>1.74659</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.46437</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>1.72207</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>1.17409</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.40407</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>1.25895</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.12572</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00092</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.15563</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02277</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03959</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01436</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04309</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04103</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04864</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.0483</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02445</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02947</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.03779</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04942</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00254</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.28018</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03564</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01187</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.0353</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20776</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.27017</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.2817</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.4523</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.42001</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>1.70016</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.45108</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.53004</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.48304</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.47569</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.54514</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.48646</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.43081</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.6003500000000001</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.60272</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.63313</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.47922</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.47644</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.5721499999999999</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.5891900000000001</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.65062</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>1.03381</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.55001</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.68123</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.56698</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.57668</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.59651</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.55596</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.46538</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.7154199999999999</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.9175800000000001</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G137" t="n">
+        <v>1.07246</v>
+      </c>
+      <c r="H137" t="n">
+        <v>1.06431</v>
+      </c>
+      <c r="I137" t="n">
+        <v>1.27107</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.83365</v>
+      </c>
+      <c r="K137" t="n">
+        <v>1.24868</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.47904</v>
+      </c>
+      <c r="M137" t="n">
+        <v>1.15143</v>
+      </c>
+      <c r="N137" t="n">
+        <v>1.17992</v>
+      </c>
+      <c r="O137" t="n">
+        <v>1.16689</v>
+      </c>
+      <c r="P137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>1.13769</v>
+      </c>
+      <c r="R137" t="n">
+        <v>1.07741</v>
+      </c>
+      <c r="S137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.57497</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>1.30801</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.7205900000000001</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.48409</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>1.15088</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.02026</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8724500000000001</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.53546</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.0342</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.15946</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.04849000000000001</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.04944</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.00311</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.29891</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32428</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30611</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-0.0429</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.31345</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25441</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29183</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.38055</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.45814</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.6552899999999999</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.71326</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.51289</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.5981300000000001</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.5664400000000001</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.71468</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.10815</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.97057</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.96882</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.97294</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.06939</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.55445</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.5605599999999999</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.5067</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.67862</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.67847</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>1.21122</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.62781</v>
+      </c>
+      <c r="H138" t="n">
+        <v>1.33351</v>
+      </c>
+      <c r="I138" t="n">
+        <v>1.03165</v>
+      </c>
+      <c r="J138" t="n">
+        <v>1.07778</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.51558</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.9847</v>
+      </c>
+      <c r="M138" t="n">
+        <v>1.29155</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.75081</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.80886</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.77404</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.90791</v>
+      </c>
+      <c r="R138" t="n">
+        <v>1.60686</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.99487</v>
+      </c>
+      <c r="T138" t="n">
+        <v>1.15601</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.9743099999999999</v>
+      </c>
+      <c r="V138" t="n">
+        <v>1.1263</v>
+      </c>
+      <c r="W138" t="n">
+        <v>1.13805</v>
+      </c>
+      <c r="X138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>1.3864</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>1.2365</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>1.11929</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>1.29856</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>1.54804</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>1.07092</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>1.13699</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.45583</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.7269600000000001</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.5628099999999999</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.27989</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.45223</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.05131</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.44399</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.10587</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.09115999999999999</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.24706</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.28368</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.29908</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.29125</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30968</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25991</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30358</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30347</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.44445</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.42494</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.4473</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.35633</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.36455</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.43763</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.45252</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.44039</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.49182</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.44643</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.5021600000000001</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.50192</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.4901</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.59927</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.60717</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.39364</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.5804900000000001</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.6197</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.5588500000000001</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.32873</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.9384199999999999</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>1.24651</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.7538899999999999</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>1.06514</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>1.04674</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.88067</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>1.48447</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.62837</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.70204</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.6458400000000001</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.69521</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.66253</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.8036599999999999</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.87682</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.78962</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.81729</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.73834</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.72502</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.7026100000000001</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.59535</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.64662</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.6277999999999999</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.62829</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.48378</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.59096</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.56751</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.47933</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.62862</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.57625</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.5724400000000001</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.57686</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.5681799999999999</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.56445</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.56452</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.6023099999999999</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.57292</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.6274</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.60468</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.62814</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.57248</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.6056</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>1.11407</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.71805</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.66443</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.5322</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.7817</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>1.28197</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.6270399999999999</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.5385700000000001</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.45058</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.44407</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.49228</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.51401</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.48986</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.53846</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.4566</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.47748</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.34087</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.41485</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.30518</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.39587</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.31187</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.45573</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.42551</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.56611</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40278</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.40994</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.95069</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.71508</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.7446499999999999</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.20393</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.6771</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.50924</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.82873</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.13042</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>1.22441</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>1.24848</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.55962</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.89558</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>1.20918</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.67879</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.50596</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.49024</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>1.01105</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.72754</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.5656599999999999</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.71849</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.6155700000000001</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.47243</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.61283</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.59841</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.6032799999999999</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.47575</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.8335900000000001</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.68587</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.74354</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.7096</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.6726799999999999</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.56223</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.6527200000000001</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.5032300000000001</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.64001</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.63776</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.6296799999999999</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.58649</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.55833</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.56165</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.56268</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.56267</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.58187</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.44518</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.59039</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.57817</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.5761799999999999</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.59005</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.47846</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.66465</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.6686</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.81497</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.6997599999999999</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.49442</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.54634</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.48554</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.48592</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.55545</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.51487</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39061</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.50238</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35335</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37927</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.49666</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.48907</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.48951</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31039</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.36554</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.5430700000000001</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.53498</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.50032</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29265</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.37507</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.5731799999999999</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.51605</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.5019</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36957</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.53465</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.5705800000000001</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.50187</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.55033</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.55204</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.61797</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.45021</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.01143</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.9053</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.72092</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.54849</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.52529</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.82511</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.81138</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.42102</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.7490399999999999</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.42009</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.79814</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.80308</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.74124</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.93767</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.91644</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.77475</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.673</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.57924</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.5793700000000001</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.57882</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.6015499999999999</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.41181</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.54553</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.49519</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.61519</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.48525</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.47521</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.6264700000000001</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.6416000000000001</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.6299199999999999</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.5665</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.4784</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.55218</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.80131</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.47837</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.46733</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.61146</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.58526</v>
+      </c>
+      <c r="S141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.58817</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.60178</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.47423</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.64034</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.4691</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.48287</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.7258</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.7323500000000001</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.51074</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.51222</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.49001</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.59649</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.5889099999999999</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.4526</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.6030800000000001</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.39989</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.46655</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.46573</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.37206</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.41087</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.23713</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.30664</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.30126</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.20561</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.18816</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.24407</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.03236</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.16231</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.30594</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.27598</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.02718</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>-0.01813</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.1632</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.18645</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.03225</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.05045</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.30626</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.27169</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.23009</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.2478</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.4383</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.45143</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.48882</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.62393</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.53625</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.46487</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.45209</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.43436</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.50897</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.41981</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.52049</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.4982799999999999</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.76916</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.51488</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.62225</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.66512</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.55737</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.56531</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.5191</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.4357799999999999</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.47087</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.55353</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.5379700000000001</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.43256</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.6268899999999999</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.48447</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.4728</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.52595</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.49475</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.52724</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.56267</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.5735</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.68709</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.5849299999999999</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.48048</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.5407799999999999</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.49177</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.5528099999999999</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.50025</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.48673</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.46928</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.47453</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.47036</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.51052</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.4786</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.47886</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.47532</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.47116</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.47308</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.46935</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.46939</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.45943</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.46512</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.46898</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.46378</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.45701</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.48594</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.44343</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.42432</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.45276</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.46008</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.46554</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.45905</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.43793</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.44929</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.40609</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.26415</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.30278</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.28364</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.14115</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.2936</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.28853</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.29163</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.23374</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.10642</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.29236</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.27274</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.42408</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.27646</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35283</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.37638</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.39956</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.46022</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.45667</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.4362</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.44675</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.4864</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.40927</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.45003</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.44953</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.48298</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.44792</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.40558</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.53846</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.59441</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.4726</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.47349</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.45761</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.49156</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.54525</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.5245599999999999</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.47626</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.46085</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.42208</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.49943</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.51103</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.43075</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.44951</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.44466</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.44365</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.44902</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.5976900000000001</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.46467</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.62802</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37299</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.45659</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.45874</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.48067</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.4896</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.47996</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.48152</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.46737</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.45523</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.51324</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.4106</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.38268</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.45544</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.48579</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.47726</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.46562</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.46238</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.44586</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.45273</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.45649</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.45787</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.39855</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.45867</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.43688</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.44429</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17682</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30251</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.28922</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14645</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19967</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.04891</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.04702000000000001</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.04733</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.13361</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>-2e-05</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03519</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.17686</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22787</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.27068</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15777</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.24248</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.04916</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.21937</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>-0.00147</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20199</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.15127</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.26422</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.27482</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.29125</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.36384</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.37692</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.4714100000000001</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.38515</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.4139</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.42364</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.40159</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.37901</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.48568</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.5885</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.5377999999999999</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.50001</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.51402</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.41296</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.47548</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.49213</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.49655</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.4604</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.48757</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.59187</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40113</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.48033</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.50262</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.47649</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.40005</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.45376</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.46189</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.45472</v>
       </c>
     </row>
   </sheetData>
